--- a/artfynd/A 42774-2026 artfynd.xlsx
+++ b/artfynd/A 42774-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137396189</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137396204</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137396208</v>
       </c>
       <c r="B4" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137396209</v>
       </c>
       <c r="B5" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>137396210</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
